--- a/DateBase/orders/Nhat 48_2026-10-21.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-21.xlsx
@@ -1213,6 +1213,9 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
       <c r="C93" t="str">
         <v>745_海芋红_Calla Lily_undefined_1bunch</v>
       </c>

--- a/DateBase/orders/Nhat 48_2026-10-21.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-21.xlsx
@@ -1290,6 +1290,9 @@
       <c r="G2" t="str">
         <v>010181042067108820208101010587971010105555151555552014622556555551557351551510728510536531151011655565101555810101051051255105105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
